--- a/ManageBookingFC/src/test/resources/Testdata/MMBData.xlsx
+++ b/ManageBookingFC/src/test/resources/Testdata/MMBData.xlsx
@@ -43,13 +43,13 @@
     <t>BookingPNR</t>
   </si>
   <si>
-    <t>RTNXDH</t>
+    <t>TWDQFW</t>
   </si>
   <si>
     <t>Firstname</t>
   </si>
   <si>
-    <t>TamilVijay</t>
+    <t>TamilKhan</t>
   </si>
   <si>
     <t>Lastname</t>
@@ -61,7 +61,7 @@
     <t>BookingActions</t>
   </si>
   <si>
-    <t>Change Flight</t>
+    <t>Manage Seats &amp; Add-ons</t>
   </si>
   <si>
     <t xml:space="preserve">MMB method selection </t>
@@ -73,7 +73,7 @@
     <t>Trip index</t>
   </si>
   <si>
-    <t>2</t>
+    <t>0</t>
   </si>
   <si>
     <t>Trip Selection for oneway OB =0, round trip IB only=1,roundtrip=2</t>
@@ -852,7 +852,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -877,7 +877,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1" quotePrefix="1">
@@ -1251,16 +1250,16 @@
       <c r="B2" s="9" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="12"/>
+      <c r="C2" s="9"/>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="13" t="s">
+      <c r="A3" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="14" t="s">
+      <c r="B3" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="12"/>
+      <c r="C3" s="9"/>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="9" t="s">
@@ -1269,7 +1268,7 @@
       <c r="B4" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="12"/>
+      <c r="C4" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1519,7 +1518,10 @@
       </c>
     </row>
   </sheetData>
-  <dataValidations count="6">
+  <dataValidations count="7">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2">
+      <formula1>"Change Flight,Manage Seats &amp; Add-ons"</formula1>
+    </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B5">
       <formula1>"0,1,2"</formula1>
     </dataValidation>
@@ -1532,7 +1534,7 @@
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B8 B11">
       <formula1>"2024,2025,2026,2027,2028,2029,2030"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B3:B4">
       <formula1>"Change Flight"</formula1>
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B15:B16">
@@ -1609,7 +1611,7 @@
       <c r="A4" t="s">
         <v>39</v>
       </c>
-      <c r="B4" s="15" t="s">
+      <c r="B4" s="14" t="s">
         <v>40</v>
       </c>
       <c r="C4" t="s">
